--- a/AAII_Financials/Quarterly/CDTG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CDTG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
   <si>
     <t>CDTG</t>
   </si>
@@ -3121,10 +3121,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2600</v>
+        <v>8800</v>
       </c>
       <c r="E59" s="3">
-        <v>2600</v>
+        <v>8800</v>
       </c>
       <c r="F59" s="3">
         <v>7800</v>
@@ -4227,11 +4227,11 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -4557,11 +4557,11 @@
       <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+      <c r="H89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-500</v>
       </c>
       <c r="J89" s="3">
         <v>-500</v>
@@ -4631,11 +4631,11 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4790,11 +4790,11 @@
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>600</v>
       </c>
       <c r="J94" s="3">
         <v>-300</v>
@@ -5076,11 +5076,11 @@
       <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+      <c r="H100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>700</v>
@@ -5117,11 +5117,11 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>100</v>
       </c>
       <c r="F101" s="3">
         <v>100</v>
